--- a/exports/MFSL_full_report.xlsx
+++ b/exports/MFSL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.76</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1014</v>
+        <v>999.5</v>
       </c>
       <c r="I2" t="n">
         <v>1000.669436</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.97</v>
+        <v>-4.35</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>4.76</v>
       </c>
       <c r="M2" t="n">
         <v>0.05</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.53</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44592.38541666666</v>
+        <v>44592.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>940.6</v>
+        <v>947.1</v>
       </c>
       <c r="I3" t="n">
         <v>944.3021329097151</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>5.89</v>
+        <v>5.24</v>
       </c>
       <c r="L3" t="n">
         <v>1.86</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44596.55208333334</v>
+        <v>44599.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>882</v>
+        <v>852.8</v>
       </c>
       <c r="I4" t="n">
         <v>863.7854312881423</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.87</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>7.03</v>
+        <v>10.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="N4" t="n">
         <v>2.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.19</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>753</v>
+        <v>774.15</v>
       </c>
       <c r="I5" t="n">
         <v>765.2340769702046</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K5" t="n">
-        <v>11.7</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>3.78</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>754.55</v>
+        <v>732</v>
       </c>
       <c r="I6" t="n">
         <v>750.0389641127822</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.53</v>
+        <v>-5.44</v>
       </c>
       <c r="L6" t="n">
-        <v>2.93</v>
+        <v>6.22</v>
       </c>
       <c r="M6" t="n">
         <v>0.2</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44707.38541666666</v>
+        <v>44707.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>755.55</v>
+        <v>766</v>
       </c>
       <c r="I7" t="n">
         <v>757.457159015742</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.22</v>
+        <v>-4.64</v>
       </c>
       <c r="L7" t="n">
         <v>6.48</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.25</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44728.55208333334</v>
+        <v>44729.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>804</v>
+        <v>782.5</v>
       </c>
       <c r="I8" t="n">
         <v>788.0282523792043</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>4.96</v>
+        <v>2.15</v>
       </c>
       <c r="L8" t="n">
         <v>2.87</v>
@@ -897,7 +992,7 @@
         <v>2.21</v>
       </c>
       <c r="N8" t="n">
-        <v>2.43</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
         <v>4.64</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>822.7</v>
+        <v>859.9</v>
       </c>
       <c r="I9" t="n">
         <v>829.9926477233389</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.14</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>6.77</v>
+        <v>10.08</v>
       </c>
       <c r="M9" t="n">
         <v>1.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>4.86</v>
       </c>
       <c r="O9" t="n">
         <v>-2.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>818.95</v>
+        <v>812</v>
       </c>
       <c r="I10" t="n">
         <v>814.6085650805788</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.76</v>
+        <v>-5.57</v>
       </c>
       <c r="L10" t="n">
-        <v>5.22</v>
+        <v>5.79</v>
       </c>
       <c r="M10" t="n">
         <v>0.01</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.85</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>856.95</v>
+        <v>877.75</v>
       </c>
       <c r="I11" t="n">
         <v>859.4845622847312</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.54</v>
+        <v>-8.1</v>
       </c>
       <c r="L11" t="n">
-        <v>8.19</v>
+        <v>8.76</v>
       </c>
       <c r="M11" t="n">
         <v>0.98</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.84</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44775.55208333334</v>
+        <v>44776.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>847</v>
+        <v>819.1</v>
       </c>
       <c r="I12" t="n">
         <v>821.8792644039705</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.5</v>
+        <v>-6.68</v>
       </c>
       <c r="L12" t="n">
-        <v>4.53</v>
+        <v>6.99</v>
       </c>
       <c r="M12" t="n">
         <v>2.28</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>814.6</v>
+        <v>838.95</v>
       </c>
       <c r="I13" t="n">
         <v>826.4137069630302</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>0.55</v>
+        <v>-2.42</v>
       </c>
       <c r="L13" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.53</v>
+        <v>3.12</v>
       </c>
       <c r="O13" t="n">
         <v>-2.64</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.1</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>810.5</v>
+        <v>791.45</v>
       </c>
       <c r="I14" t="n">
         <v>802.590556670704</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.39</v>
+        <v>-5.66</v>
       </c>
       <c r="L14" t="n">
         <v>6.55</v>
@@ -1239,7 +1406,7 @@
         <v>0.72</v>
       </c>
       <c r="N14" t="n">
-        <v>3.41</v>
+        <v>3.82</v>
       </c>
       <c r="O14" t="n">
         <v>3.12</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>7.74</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44890.55208333334</v>
+        <v>44893.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>665.4</v>
+        <v>688.2</v>
       </c>
       <c r="I15" t="n">
         <v>677.989344714154</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>66</v>
       </c>
       <c r="K15" t="n">
-        <v>15.93</v>
+        <v>13.05</v>
       </c>
       <c r="L15" t="n">
         <v>3.16</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
         <v>3.16</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44918.38541666666</v>
+        <v>44918.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>681.25</v>
+        <v>672.95</v>
       </c>
       <c r="I16" t="n">
         <v>680.1693650070532</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.01</v>
+        <v>-2.22</v>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>3.17</v>
       </c>
       <c r="M16" t="n">
         <v>1.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.86</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44928.55208333334</v>
+        <v>44929.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>685.4</v>
+        <v>709.65</v>
       </c>
       <c r="I17" t="n">
         <v>708.5287284482835</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.85</v>
+        <v>-5.45</v>
       </c>
       <c r="L17" t="n">
-        <v>2.58</v>
+        <v>5.87</v>
       </c>
       <c r="M17" t="n">
         <v>0.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.08</v>
+        <v>3.38</v>
       </c>
       <c r="O17" t="n">
         <v>-2.16</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>834.5</v>
+        <v>794.1</v>
       </c>
       <c r="I18" t="n">
         <v>816.8724456598223</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>17.59</v>
+        <v>11.9</v>
       </c>
       <c r="L18" t="n">
         <v>4.5</v>
@@ -1467,7 +1682,7 @@
         <v>1.56</v>
       </c>
       <c r="N18" t="n">
-        <v>4.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>3.38</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.56</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45049.55208333334</v>
+        <v>45050.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>639.05</v>
+        <v>651.95</v>
       </c>
       <c r="I19" t="n">
         <v>647.4985519525302</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>91.16666666666667</v>
+        <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>19.53</v>
+        <v>17.9</v>
       </c>
       <c r="L19" t="n">
         <v>8.119999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>679.9</v>
+        <v>677.45</v>
       </c>
       <c r="I20" t="n">
         <v>677.9403006089893</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>4.29</v>
+        <v>3.91</v>
       </c>
       <c r="L20" t="n">
         <v>3.05</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.86</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45096.55208333334</v>
+        <v>45097.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>688</v>
+        <v>704.15</v>
       </c>
       <c r="I21" t="n">
         <v>703.8340984618776</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.56</v>
+        <v>-3.94</v>
       </c>
       <c r="L21" t="n">
-        <v>2.98</v>
+        <v>4.71</v>
       </c>
       <c r="M21" t="n">
         <v>0.45</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>807.95</v>
+        <v>776.55</v>
       </c>
       <c r="I22" t="n">
         <v>796.5854902786099</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
-        <v>14.74</v>
+        <v>10.28</v>
       </c>
       <c r="L22" t="n">
         <v>3.49</v>
@@ -1695,7 +1958,7 @@
         <v>1.32</v>
       </c>
       <c r="N22" t="n">
-        <v>2.43</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>2.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45146.38541666666</v>
+        <v>45146.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>799.95</v>
+        <v>811.7</v>
       </c>
       <c r="I23" t="n">
         <v>810.9886783167199</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.01</v>
+        <v>-4.53</v>
       </c>
       <c r="L23" t="n">
         <v>4.86</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>908.85</v>
+        <v>905</v>
       </c>
       <c r="I24" t="n">
         <v>905.0697600285993</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50.83333333333334</v>
+        <v>51</v>
       </c>
       <c r="K24" t="n">
-        <v>11.97</v>
+        <v>11.49</v>
       </c>
       <c r="L24" t="n">
         <v>3.27</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.77</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>921.65</v>
+        <v>938</v>
       </c>
       <c r="I25" t="n">
         <v>923.0572919593559</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.84</v>
+        <v>-3.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2.58</v>
+        <v>3.92</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>5.7</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>899.2</v>
+        <v>883.8</v>
       </c>
       <c r="I26" t="n">
         <v>897.641868120234</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.14</v>
+        <v>-5.78</v>
       </c>
       <c r="L26" t="n">
-        <v>4.45</v>
+        <v>6.24</v>
       </c>
       <c r="M26" t="n">
         <v>0.14</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.37</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>920.7</v>
+        <v>926.1</v>
       </c>
       <c r="I27" t="n">
         <v>922.8714000678732</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.18</v>
+        <v>-4.79</v>
       </c>
       <c r="L27" t="n">
-        <v>4.22</v>
+        <v>4.88</v>
       </c>
       <c r="M27" t="n">
         <v>0.7</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>5.65</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>887.95</v>
+        <v>878</v>
       </c>
       <c r="I28" t="n">
         <v>879.1964234015294</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.12</v>
+        <v>-5.19</v>
       </c>
       <c r="L28" t="n">
         <v>5.81</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.38</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>915</v>
+        <v>942.95</v>
       </c>
       <c r="I29" t="n">
         <v>941.7993615260679</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>11</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.21</v>
+        <v>-7.4</v>
       </c>
       <c r="L29" t="n">
-        <v>7.45</v>
+        <v>7.72</v>
       </c>
       <c r="M29" t="n">
         <v>0.97</v>
       </c>
       <c r="N29" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>-1.23</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1024.85</v>
+        <v>978.75</v>
       </c>
       <c r="I30" t="n">
         <v>1014.458645412642</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K30" t="n">
-        <v>8.69</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>3.45</v>
@@ -2151,7 +2510,7 @@
         <v>0.11</v>
       </c>
       <c r="N30" t="n">
-        <v>3.04</v>
+        <v>4.86</v>
       </c>
       <c r="O30" t="n">
         <v>2.95</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>915</v>
+        <v>946.8</v>
       </c>
       <c r="I31" t="n">
         <v>921.6727337986715</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K31" t="n">
-        <v>6.51</v>
+        <v>3.26</v>
       </c>
       <c r="L31" t="n">
         <v>5.15</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="N31" t="n">
         <v>5.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>997</v>
+        <v>974.55</v>
       </c>
       <c r="I32" t="n">
         <v>994.7636627748844</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>2.93</v>
       </c>
       <c r="L32" t="n">
         <v>3.56</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>965.5</v>
+        <v>992.25</v>
       </c>
       <c r="I33" t="n">
         <v>978.9885505243744</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K33" t="n">
-        <v>0.93</v>
+        <v>-1.82</v>
       </c>
       <c r="L33" t="n">
         <v>6.55</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.44</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45517.55208333334</v>
+        <v>45518.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="I34" t="n">
         <v>1051.074868392182</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K34" t="n">
-        <v>6.32</v>
+        <v>5.32</v>
       </c>
       <c r="L34" t="n">
         <v>5.25</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>5.38</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1074.5</v>
+        <v>1092.15</v>
       </c>
       <c r="I35" t="n">
         <v>1086.509532308536</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.82</v>
+        <v>-4.51</v>
       </c>
       <c r="L35" t="n">
-        <v>4.38</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>0.45</v>
+        <v>1.14</v>
       </c>
       <c r="N35" t="n">
         <v>3.32</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1218.8</v>
+        <v>1211</v>
       </c>
       <c r="I36" t="n">
         <v>1212.71734733263</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K36" t="n">
-        <v>11.6</v>
+        <v>10.88</v>
       </c>
       <c r="L36" t="n">
         <v>1.48</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1065.2</v>
+        <v>1091.95</v>
       </c>
       <c r="I37" t="n">
         <v>1090.47573181762</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K37" t="n">
-        <v>12.04</v>
+        <v>9.83</v>
       </c>
       <c r="L37" t="n">
         <v>2.81</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.6</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1054</v>
+        <v>1044.4</v>
       </c>
       <c r="I38" t="n">
         <v>1044.581500432691</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.48</v>
+        <v>-4.35</v>
       </c>
       <c r="L38" t="n">
         <v>6.64</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1035.5</v>
+        <v>1044.3</v>
       </c>
       <c r="I39" t="n">
         <v>1043.556235362756</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>0.85</v>
+        <v>0.01</v>
       </c>
       <c r="L39" t="n">
         <v>2.07</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.39</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1611.5</v>
+        <v>1581.6</v>
       </c>
       <c r="I40" t="n">
         <v>1582.872760742833</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>115.1666666666667</v>
+        <v>116</v>
       </c>
       <c r="K40" t="n">
-        <v>54.31</v>
+        <v>51.45</v>
       </c>
       <c r="L40" t="n">
         <v>9.029999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.86</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45877.38541666666</v>
+        <v>45877.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1534</v>
+        <v>1545</v>
       </c>
       <c r="I41" t="n">
         <v>1534.845896037101</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>3.01</v>
+        <v>2.31</v>
       </c>
       <c r="L41" t="n">
         <v>2.69</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.02</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1620</v>
+        <v>1570.8</v>
       </c>
       <c r="I42" t="n">
         <v>1582.555162066872</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>4.85</v>
+        <v>1.67</v>
       </c>
       <c r="L42" t="n">
         <v>1.29</v>
@@ -2835,7 +3338,7 @@
         <v>0.75</v>
       </c>
       <c r="N42" t="n">
-        <v>1.21</v>
+        <v>3.19</v>
       </c>
       <c r="O42" t="n">
         <v>2.58</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.84</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1580</v>
+        <v>1615</v>
       </c>
       <c r="I43" t="n">
         <v>1603.515840889345</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.59</v>
+        <v>-2.81</v>
       </c>
       <c r="L43" t="n">
         <v>5.86</v>
@@ -2892,7 +3407,7 @@
         <v>2.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="O43" t="n">
         <v>-3.19</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.28</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1607.7</v>
+        <v>1555.9</v>
       </c>
       <c r="I44" t="n">
         <v>1557.536723354052</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.45</v>
+        <v>-3.66</v>
       </c>
       <c r="L44" t="n">
         <v>4.02</v>
@@ -2949,7 +3476,7 @@
         <v>0.89</v>
       </c>
       <c r="N44" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>2.41</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.94</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1558.8</v>
+        <v>1593.5</v>
       </c>
       <c r="I45" t="n">
         <v>1575.4955999894</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.19</v>
+        <v>-2.42</v>
       </c>
       <c r="L45" t="n">
         <v>2.83</v>
@@ -3006,7 +3545,7 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="O45" t="n">
         <v>-3.15</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.27</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46007.55208333334</v>
+        <v>46008.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1663.2</v>
+        <v>1649.7</v>
       </c>
       <c r="I46" t="n">
         <v>1654.332041530101</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>4.37</v>
+        <v>3.53</v>
       </c>
       <c r="L46" t="n">
         <v>2.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.7</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1677</v>
+        <v>1724.3</v>
       </c>
       <c r="I47" t="n">
         <v>1718.925128523487</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.65</v>
+        <v>-4.52</v>
       </c>
       <c r="L47" t="n">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="M47" t="n">
         <v>1.12</v>
       </c>
       <c r="N47" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="O47" t="n">
         <v>0.03</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.28</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1650.3</v>
+        <v>1633.8</v>
       </c>
       <c r="I48" t="n">
         <v>1642.469413688929</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.29</v>
+        <v>-5.25</v>
       </c>
       <c r="L48" t="n">
         <v>5.61</v>
@@ -3177,7 +3752,7 @@
         <v>0.85</v>
       </c>
       <c r="N48" t="n">
-        <v>1.52</v>
+        <v>2.01</v>
       </c>
       <c r="O48" t="n">
         <v>1.91</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>5.45</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1640</v>
+        <v>1677.3</v>
       </c>
       <c r="I49" t="n">
         <v>1655.59005187202</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.38</v>
+        <v>-2.66</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>3.11</v>
       </c>
       <c r="M49" t="n">
-        <v>0.68</v>
+        <v>1.43</v>
       </c>
       <c r="N49" t="n">
         <v>3.17</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.88</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1805.2</v>
+        <v>1729.2</v>
       </c>
       <c r="I50" t="n">
         <v>1792.007063420051</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K50" t="n">
-        <v>7.63</v>
+        <v>3.09</v>
       </c>
       <c r="L50" t="n">
         <v>1.35</v>
@@ -3291,7 +3890,7 @@
         <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.77</v>
+        <v>3.21</v>
       </c>
       <c r="O50" t="n">
         <v>2.05</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1481.8</v>
+        <v>1615.2</v>
       </c>
       <c r="I51" t="n">
         <v>1573.813509830317</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>14.31</v>
+        <v>6.59</v>
       </c>
       <c r="L51" t="n">
         <v>3.22</v>
       </c>
       <c r="M51" t="n">
-        <v>2.67</v>
+        <v>4.6</v>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>7.16</v>
       </c>
       <c r="O51" t="n">
         <v>-3.21</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1592.5</v>
+        <v>1577.3</v>
       </c>
       <c r="I52" t="n">
         <v>1589.82629785668</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.41</v>
+        <v>-2.35</v>
       </c>
       <c r="L52" t="n">
         <v>5.92</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.79</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1653.7</v>
+        <v>1696</v>
       </c>
       <c r="I53" t="n">
         <v>1668.693364834185</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.84</v>
+        <v>-7.53</v>
       </c>
       <c r="L53" t="n">
-        <v>5.05</v>
+        <v>7.78</v>
       </c>
       <c r="M53" t="n">
         <v>0.91</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.01</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1620.6</v>
+        <v>1601</v>
       </c>
       <c r="I54" t="n">
         <v>1613.290858100888</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.45</v>
+        <v>-5.6</v>
       </c>
       <c r="L54" t="n">
-        <v>5.04</v>
+        <v>6.24</v>
       </c>
       <c r="M54" t="n">
         <v>0.07000000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.87</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46164.38541666666</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1669.1</v>
+        <v>1685</v>
       </c>
       <c r="I55" t="n">
         <v>1684.001497525024</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.25</v>
+        <v>-5.25</v>
       </c>
       <c r="L55" t="n">
-        <v>4.45</v>
+        <v>5.38</v>
       </c>
       <c r="M55" t="n">
         <v>0.87</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.25</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1646.5</v>
+        <v>1620</v>
       </c>
       <c r="I56" t="n">
         <v>1633.282631720726</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.28</v>
+        <v>-3.86</v>
       </c>
       <c r="L56" t="n">
-        <v>2.43</v>
+        <v>3.94</v>
       </c>
       <c r="M56" t="n">
         <v>0.13</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1633.2</v>
+        <v>1665.3</v>
       </c>
       <c r="I57" t="n">
         <v>1651.28896263993</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.8</v>
       </c>
       <c r="L57" t="n">
-        <v>2.41</v>
+        <v>3.7</v>
       </c>
       <c r="M57" t="n">
         <v>0.68</v>
       </c>
       <c r="N57" t="n">
-        <v>2.51</v>
+        <v>3.29</v>
       </c>
       <c r="O57" t="n">
         <v>-2.71</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1619</v>
+        <v>1581.3</v>
       </c>
       <c r="I58" t="n">
         <v>1602.254321158638</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.78</v>
+        <v>-5.04</v>
       </c>
       <c r="L58" t="n">
-        <v>3.44</v>
+        <v>6.09</v>
       </c>
       <c r="M58" t="n">
         <v>0.63</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.68</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46251.38541666666</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1563.3</v>
+        <v>1567</v>
       </c>
       <c r="I59" t="n">
         <v>1564.442935475889</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="L59" t="n">
         <v>5.1</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.43</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1525</v>
+        <v>1520.5</v>
       </c>
       <c r="I60" t="n">
         <v>1520.828522662038</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.68</v>
+        <v>-2.97</v>
       </c>
       <c r="L60" t="n">
-        <v>2.68</v>
+        <v>4.66</v>
       </c>
       <c r="M60" t="n">
         <v>0.35</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.36</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1480.5</v>
+        <v>1563.1</v>
       </c>
       <c r="I61" t="n">
         <v>1510.424749306056</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>2.63</v>
+        <v>-2.8</v>
       </c>
       <c r="L61" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="M61" t="n">
         <v>0.43</v>
       </c>
       <c r="N61" t="n">
-        <v>3.42</v>
+        <v>4.69</v>
       </c>
       <c r="O61" t="n">
         <v>-0.66</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1557.4</v>
+        <v>1398.3</v>
       </c>
       <c r="I62" t="n">
         <v>1481.10110349515</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.36</v>
+        <v>-10.54</v>
       </c>
       <c r="L62" t="n">
-        <v>5.73</v>
+        <v>12.99</v>
       </c>
       <c r="M62" t="n">
-        <v>0.74</v>
+        <v>9.68</v>
       </c>
       <c r="N62" t="n">
-        <v>0.89</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O62" t="n">
         <v>4.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>44</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6900,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6910,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6920,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6930,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6940,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6950,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -6227,7 +6990,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.46</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +7000,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.26</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7010,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.63</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7020,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.31</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7030,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.6</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7040,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7050,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.68</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="21">
@@ -6297,7 +7060,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.029999999999999</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="22">
@@ -6307,7 +7070,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7080,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7090,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="25">
@@ -6337,7 +7100,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.7</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="26">
@@ -6347,7 +7110,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +7120,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.77</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6367,7 +7130,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
